--- a/aq_files/0642.xlsx
+++ b/aq_files/0642.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,877 +424,477 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Options</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Explanation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lakehouse combines:</t>
+          <t>What is horizontal scaling?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DB+API</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Data lake + warehouse</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OLTP+OLAP</t>
+          <t>Horizontal scaling adds more machines to distribute load.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Supports data types:</t>
+          <t>What is the difference between horizontal and vertical scaling?</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Structured</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Unstructured</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Semi-structured</t>
+          <t>Horizontal adds nodes; vertical adds resources to single node.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Schema-on-read is typical of:</t>
+          <t>What distributed processing framework is written in Python?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DW</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lakehouse</t>
+          <t>PySpark is Python API for Apache Spark.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Example platform:</t>
+          <t>What is a Spark cluster?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MySQL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Delta Lake</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>A cluster consists of a master and worker nodes.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lakehouse supports:</t>
+          <t>What is the purpose of data partitioning in Spark?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OLTP</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>OLAP</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Partitions enable parallel data processing.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ACID ensures:</t>
+          <t>Scenario: A pipeline processing 100GB daily takes 4 hours. How to scale?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>Scenario-based</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>A) Use larger VM,B) Implement distributed processing,C) Optimize queries,D) All of the above</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Multiple scaling strategies work together.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Networking</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Storage is typically:</t>
+          <t>What is the default parallelism level in Spark?</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Expensive</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Cheap/object storage</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Default parallelism equals number of cores.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unified analytics means:</t>
+          <t>What is the purpose of a distributed message queue?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Single tool only</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Integrated analytics across workloads</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No integration</t>
+          <t>Message queues like Kafka handle data streaming.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Versioning enables:</t>
+          <t>What does Apache Kafka provide for data pipelines?</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deletion</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Tracking changes</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Duplication</t>
+          <t>Kafka is a distributed streaming platform.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Time travel enables:</t>
+          <t>What is the difference between Kafka and RabbitMQ?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Future access</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Past snapshots</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deletion</t>
+          <t>Kafka stores data; RabbitMQ routes messages.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Schema enforcement ensures:</t>
+          <t>What is the purpose of connection pooling?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Flexibility</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Data quality</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>Connection pooling improves database performance.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Supports ML workloads:</t>
+          <t>What is the recommended approach for handling secrets in scalable pipelines?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Use tools like AWS Secrets Manager or HashiCorp Vault.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Governance ensures:</t>
+          <t>What is the purpose of a data lake?</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Security &amp; control</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Speed</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Data lakes store raw data in native format.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Typical storage:</t>
+          <t>What is the difference between a data lake and a data warehouse?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Local only</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Cloud/object store</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tape</t>
+          <t>Data lakes store raw; warehouses store processed data.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Need both BI dashboards and ML on same data with ACID guarantees. Choose:</t>
+          <t>Scenario: A pipeline fails when data volume spikes to 5x normal. What's needed?</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>Scenario-based</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>A) Auto-scaling,B) Fixed capacity,C) Manual intervention,D) Data sampling</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lakehouse</t>
+          <t>Auto-scaling adjusts resources based on load.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cache</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Team queries raw files first and applies schema at read time. Choose:</t>
+          <t>What is the purpose of retry logic in pipelines?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DW</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lakehouse/Lake</t>
+          <t>Retries handle transient failures automatically.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cache</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Need rollback to previous table version after bad update. Feature?</t>
+          <t>What is circuit breaker pattern?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sharding</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Time travel/versioning</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Caching</t>
+          <t>Circuit breakers prevent cascading failures.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Replication</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Need low-cost storage for large datasets with analytics. Choose:</t>
+          <t>What is the purpose of a dead letter queue?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DW only</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Lakehouse</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DB only</t>
+          <t>DLQ stores messages that failed processing.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cache</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ensure transactional consistency on data lake tables. Choose tech:</t>
+          <t>How does batch size affect pipeline performance?</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Plain S3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Delta Lake/Iceberg</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CSV only</t>
+          <t>Optimal batch size balances latency and throughput.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FTP</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Enforce schema to prevent bad writes while keeping flexibility. Choose:</t>
+          <t>Scenario: A company needs to process real-time analytics. Which architecture is appropriate?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>No schema</t>
+          <t>Scenario-based</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Schema enforcement</t>
+          <t>A) Batch processing only,B) Streaming architecture with Kafka and Spark Streaming,C) Manual ETL,D) Single server</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Manual checks</t>
+          <t>Streaming architecture enables real-time processing.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
